--- a/faculty_assignment_ODD.xlsx
+++ b/faculty_assignment_ODD.xlsx
@@ -2,28 +2,38 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="4545" windowWidth="21705" windowHeight="8580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ME" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,12 +47,42 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -55,14 +95,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,106 +471,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>nick_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>emp_code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>dept_origin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>deptL_class</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>semL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>L_code</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>L_class</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>L_hr</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>deptT_class</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>semT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>T_code</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>T_hr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>deptP_class</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>semP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>P_code</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>P_hr</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>deptR_class</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>semR</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>R_code</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>R_hr</t>
         </is>
@@ -546,37 +592,63 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GAMAT101</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>GAMAT101</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>CE,CE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>s1,s1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GAMAT101,GAPHT121</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>GAPHT121,GMEST103</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -585,46 +657,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZADIE</t>
+          <t>ZVL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>s1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>UCHUT128</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GXEST104</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>CE,CE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>GAPHT121,GMEST103</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
@@ -633,51 +719,339 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZVL</t>
+          <t>ELVIZ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GMEST103</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CE,CE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>GAMAT101,GXEST104</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1.0,1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>CE,CE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>GXESL106,UCEST105</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NIVI</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CE,CE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>UCEST105,GXESL106</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ZADIE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1009</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>UCHUT128</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CE,ME</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>GAPHT121,GMEST103</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EZRI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>GAMAT101</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nick_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>emp_code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dept_origin</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>deptL_class</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>semL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>L_code</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>L_class</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>L_hr</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>deptT_class</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>semT</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>T_code</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T_hr</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>deptP_class</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>semP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>P_code</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>P_hr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>deptR_class</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>semR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>R_code</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>R_hr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/faculty_assignment_ODD.xlsx
+++ b/faculty_assignment_ODD.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -631,22 +631,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CE,CE</t>
+          <t>CE,CE,CE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>s1,s1</t>
+          <t>s1,s1,s1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GAPHT121,GMEST103</t>
+          <t>GAPHT121,GMEST103,UCEST105</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -668,47 +668,65 @@
           <t>CE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UCHUT128</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>CE,CE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s1,s1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GXEST104</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
+          <t>UCHUT128,GXEST104</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.0,1</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CE,CE</t>
+          <t>CE,CE,CE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>s1,s1</t>
+          <t>s1,s1,s1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GAPHT121,GMEST103</t>
+          <t>GMEST103,GAPHT121,UCEST105</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -719,60 +737,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELVIZ</t>
+          <t>ZADIE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CE,CE</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>s1,s1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>GAMAT101,GXEST104</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.0,1</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>UCEST105</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CE,CE</t>
+          <t>CE,ME,CE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>s1,s1</t>
+          <t>s1,s1,s1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GXESL106,UCEST105</t>
+          <t>GXESL106,GXESL106,GAPHT121</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -783,11 +801,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIVI</t>
+          <t>EZER</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -805,22 +823,22 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CE,CE</t>
+          <t>CE,CE,ME,CE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>s1,s1</t>
+          <t>s1,s1,s1,s1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>UCEST105,GXESL106</t>
+          <t>UCEST105,GXESL106,GAPHT121,GMEST103</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,1,1,1</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -831,43 +849,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZADIE</t>
+          <t>NIVI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>s1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>UCHUT128</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GAPHT121</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CE,ME</t>
+          <t>CE,CE</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -877,7 +897,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GAPHT121,GMEST103</t>
+          <t>GAPHT121,GXESL106</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -904,37 +924,197 @@
           <t>CE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>s1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>GAMAT101</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GMEST103</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>CE,CE,CE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>s1,s1,s1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>UCEST105,GXESL106,GMEST103</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ELVIZ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CE,CE</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GXEST104,GAMAT101</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHINO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>GAMAT101</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ANJANA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GXEST104</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
